--- a/artfynd/A 57145-2024 artfynd.xlsx
+++ b/artfynd/A 57145-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123804256</v>
       </c>
       <c r="B2" t="n">
-        <v>79897</v>
+        <v>79902</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 57145-2024 artfynd.xlsx
+++ b/artfynd/A 57145-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123804256</v>
       </c>
       <c r="B2" t="n">
-        <v>79902</v>
+        <v>79904</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 57145-2024 artfynd.xlsx
+++ b/artfynd/A 57145-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>123804256</v>
       </c>
       <c r="B2" t="n">
-        <v>79926</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,6 +793,215 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123804892</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Norumshöjden, Norumshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>426110</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6601418</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jonas Sjöblom</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jonas Sjöblom</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123804566</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norumshöjden, Norumshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>426142</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6601442</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt i slänten</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57145-2024 artfynd.xlsx
+++ b/artfynd/A 57145-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123804256</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123804892</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,8 +1017,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123804566</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>